--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
@@ -39,24 +39,24 @@
     <t xml:space="preserve">San Juan de la Costa</t>
   </si>
   <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maullín</t>
   </si>
   <si>
-    <t xml:space="preserve">Cochamó</t>
+    <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
-    <t xml:space="preserve">San Pablo</t>
+    <t xml:space="preserve">Quemchi</t>
   </si>
   <si>
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quinchao</t>
   </si>
   <si>
@@ -81,24 +81,24 @@
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
     <t xml:space="preserve">Llanquihue</t>
   </si>
   <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chonchi</t>
   </si>
   <si>
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Dalcahue</t>
   </si>
   <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
-    <t xml:space="preserve">Castro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>177.5</v>
+        <v>194.95</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>10108</v>
+        <v>10103</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>159.91</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="4">
@@ -596,13 +596,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10103</v>
+        <v>10108</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>158.75</v>
+        <v>171.07</v>
       </c>
     </row>
     <row r="5">
@@ -613,13 +613,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10206</v>
+        <v>10307</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>156.56</v>
+        <v>166.86</v>
       </c>
     </row>
     <row r="6">
@@ -630,13 +630,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10307</v>
+        <v>10206</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>154.86</v>
+        <v>165.8</v>
       </c>
     </row>
     <row r="7">
@@ -647,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10104</v>
+        <v>10209</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>148.48</v>
+        <v>161.93</v>
       </c>
     </row>
     <row r="8">
@@ -664,13 +664,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10209</v>
+        <v>10104</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>148.23</v>
+        <v>161.85</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>144.23</v>
+        <v>158.39</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>143</v>
+        <v>153.48</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>140.33</v>
+        <v>152.56</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>139.8</v>
+        <v>150.05</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>134.3</v>
+        <v>145.05</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>131.5</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="15">
@@ -789,7 +789,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>130.34</v>
+        <v>141.79</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>129.51</v>
+        <v>139.94</v>
       </c>
     </row>
     <row r="17">
@@ -817,13 +817,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10401</v>
+        <v>10207</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>124.9</v>
+        <v>137.05</v>
       </c>
     </row>
     <row r="18">
@@ -834,13 +834,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>10207</v>
+        <v>10401</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>124.36</v>
+        <v>133.95</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>123.07</v>
+        <v>133.36</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>115.25</v>
+        <v>124.31</v>
       </c>
     </row>
     <row r="21">
@@ -885,13 +885,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10301</v>
+        <v>10102</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>111.26</v>
+        <v>121.33</v>
       </c>
     </row>
     <row r="22">
@@ -902,13 +902,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>10102</v>
+        <v>10301</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>111.01</v>
+        <v>120.11</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>106.71</v>
+        <v>115.05</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>100.28</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>98.81</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>95.5</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="27">
@@ -987,13 +987,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10402</v>
+        <v>10201</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>94.93</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="28">
@@ -1004,13 +1004,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10201</v>
+        <v>10402</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>94.75</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>84.32</v>
+        <v>90.72</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>77.31</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>67.52</v>
+        <v>72.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:27</t>
+    <t xml:space="preserve">2026-10-05 16:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
